--- a/press/nyctotype/NyctoType_Press_Release_Media_List.xlsx
+++ b/press/nyctotype/NyctoType_Press_Release_Media_List.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="送付先一覧" sheetId="1" r:id="R7fa4c49862c24ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="R95766d7df3824066"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="送付先一覧" sheetId="1" r:id="R5f05b9cabc094049"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="R2590a8d3ac744460"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -406,8 +406,8 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="4" t="str">
-        <x:f>"登録 "&amp;COUNTA($D$9:$D$63)&amp;"媒体（必須 "&amp;COUNTIFS($B$9:$B$63,"必須")&amp;"媒体） / 送付済み "&amp;COUNTIFS($L$9:$L$63,"送付済み")&amp;" / 掲載 "&amp;COUNTIFS($N$9:$N$63,"掲載")&amp;" / 基準日 2026-09-12"</x:f>
-        <x:v>登録 55媒体（必須 12媒体） / 送付済み 0 / 掲載 0 / 基準日 2026-09-12</x:v>
+        <x:f>"登録 "&amp;COUNTA($D$9:$D$63)&amp;"媒体（必須 "&amp;COUNTIFS($B$9:$B$63,"必須")&amp;"媒体） / 送付済み "&amp;COUNTIFS($L$9:$L$63,"送付済み")&amp;" / 掲載 "&amp;COUNTIFS($N$9:$N$63,"掲載")&amp;" / 基準日 2026-09-16"</x:f>
+        <x:v>登録 55媒体（必須 12媒体） / 送付済み 15 / 掲載 1 / 基準日 2026-09-16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
@@ -546,9 +546,11 @@
         <x:v>S1 / S2 / S3 / S4 / S5</x:v>
       </x:c>
       <x:c r="L10" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M10" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M10" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N10" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
@@ -590,9 +592,11 @@
         <x:v>S1 / S2 / S3 / S5</x:v>
       </x:c>
       <x:c r="L11" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M11" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M11" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N11" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
@@ -634,9 +638,11 @@
         <x:v>S1 / S2 / S4</x:v>
       </x:c>
       <x:c r="L12" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M12" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M12" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N12" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
@@ -678,9 +684,11 @@
         <x:v>S1 / S2 / S4 / S5 / S6</x:v>
       </x:c>
       <x:c r="L13" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M13" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M13" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N13" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
@@ -724,9 +732,11 @@
         <x:v>S1 / S2 / S3 / S4</x:v>
       </x:c>
       <x:c r="L14" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M14" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M14" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N14" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
@@ -768,9 +778,11 @@
         <x:v>S2 / S4</x:v>
       </x:c>
       <x:c r="L15" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M15" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M15" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N15" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
@@ -812,9 +824,11 @@
         <x:v>S1</x:v>
       </x:c>
       <x:c r="L16" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M16" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M16" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N16" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
@@ -858,15 +872,19 @@
         <x:v>S1 / S2 / S3 / S4 / S5</x:v>
       </x:c>
       <x:c r="L17" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M17" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M17" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N17" s="8" t="str">
-        <x:v>未確認</x:v>
-      </x:c>
-      <x:c r="O17" s="8" t="str"/>
+        <x:v>掲載</x:v>
+      </x:c>
+      <x:c r="O17" s="8" t="str">
+        <x:v>https://www.famitsu.com/article/202609/87998</x:v>
+      </x:c>
       <x:c r="P17" s="8" t="str">
-        <x:v>実送付例で当日掲載実績あり</x:v>
+        <x:v>2026-09-15 19:30掲載（送付当日）</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
@@ -904,9 +922,11 @@
         <x:v>S1 / S2 / S3 / S4</x:v>
       </x:c>
       <x:c r="L18" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M18" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M18" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N18" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
@@ -948,9 +968,11 @@
         <x:v>S1 / S2</x:v>
       </x:c>
       <x:c r="L19" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M19" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M19" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N19" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
@@ -992,9 +1014,11 @@
         <x:v>S1 / S2 / S4 / S5</x:v>
       </x:c>
       <x:c r="L20" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M20" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M20" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N20" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
@@ -1036,9 +1060,11 @@
         <x:v>S1 / S2 / S3 / S4 / S5</x:v>
       </x:c>
       <x:c r="L21" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M21" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M21" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N21" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
@@ -1080,9 +1106,11 @@
         <x:v>S3 / S4</x:v>
       </x:c>
       <x:c r="L22" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M22" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M22" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N22" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
@@ -1106,10 +1134,10 @@
         <x:v>インディーゲームのニュース掲載を受け付けるコミュニティ媒体</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>フォーム</x:v>
+        <x:v>メール</x:v>
       </x:c>
       <x:c r="G23" s="8" t="str">
-        <x:v>公式フォーム</x:v>
+        <x:v>info@gamewriter.jp</x:v>
       </x:c>
       <x:c r="H23" s="8" t="str">
         <x:v>https://gamewriter.jp/ニュース掲載/</x:v>
@@ -1124,15 +1152,17 @@
         <x:v>S3 / S4</x:v>
       </x:c>
       <x:c r="L23" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M23" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M23" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N23" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
       <x:c r="O23" s="8" t="str"/>
       <x:c r="P23" s="8" t="str">
-        <x:v>実送付例で掲載実績あり</x:v>
+        <x:v>ニュース掲載フォームが動作しなかったため、案内に従いinfo@gamewriter.jpへ送付</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="24" hidden="0" customHeight="1">
@@ -1624,9 +1654,11 @@
         <x:v>S8</x:v>
       </x:c>
       <x:c r="L34" s="8" t="str">
-        <x:v>未送付</x:v>
-      </x:c>
-      <x:c r="M34" s="9"/>
+        <x:v>送付済み</x:v>
+      </x:c>
+      <x:c r="M34" s="9" t="n">
+        <x:v>46280</x:v>
+      </x:c>
       <x:c r="N34" s="8" t="str">
         <x:v>未確認</x:v>
       </x:c>
@@ -2975,7 +3007,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c388e4a68b4495"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb059ed97745a46ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3216,7 +3248,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a3b8ecba00d471d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c7621e53d044599"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/press/nyctotype/NyctoType_Press_Release_Media_List.xlsx
+++ b/press/nyctotype/NyctoType_Press_Release_Media_List.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="送付先一覧" sheetId="1" r:id="R5f05b9cabc094049"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="R2590a8d3ac744460"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="送付先一覧" sheetId="1" r:id="Rd761e2ca87fe49b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="Ra05d078c690f4ff4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1226,19 +1226,19 @@
         <x:v>個人開発・スマホ寄りだが、独自性のあるゲームを扱う</x:v>
       </x:c>
       <x:c r="F25" s="8" t="str">
-        <x:v>案内ページ</x:v>
+        <x:v>メール</x:v>
       </x:c>
       <x:c r="G25" s="8" t="str">
-        <x:v>公式案内を確認</x:v>
+        <x:v>gamecastblog@gmail.com</x:v>
       </x:c>
       <x:c r="H25" s="8" t="str">
-        <x:v>http://www.gamecast-blog.com/archives/65836087.html</x:v>
+        <x:v>https://www.gamecast-blog.com/archives/65836087.html</x:v>
       </x:c>
       <x:c r="I25" s="8" t="str">
         <x:v>http://www.gamecast-blog.com/</x:v>
       </x:c>
       <x:c r="J25" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>送付可</x:v>
       </x:c>
       <x:c r="K25" s="8" t="str">
         <x:v>S2</x:v>
@@ -1252,7 +1252,7 @@
       </x:c>
       <x:c r="O25" s="8" t="str"/>
       <x:c r="P25" s="8" t="str">
-        <x:v>PC向けNyctoTypeとの適合は送付前に再確認</x:v>
+        <x:v>公式案内でリリース前・日本のインディー・有料ゲームを歓迎。2026-09-16確認</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
@@ -1318,10 +1318,10 @@
         <x:v>日本発ゲームを英語で扱う海外媒体</x:v>
       </x:c>
       <x:c r="F27" s="8" t="str">
-        <x:v>案内ページ</x:v>
+        <x:v>メール</x:v>
       </x:c>
       <x:c r="G27" s="8" t="str">
-        <x:v>公式案内を確認</x:v>
+        <x:v>editor@gematsu.com</x:v>
       </x:c>
       <x:c r="H27" s="8" t="str">
         <x:v>https://www.gematsu.com/about</x:v>
@@ -1330,7 +1330,7 @@
         <x:v>https://www.gematsu.com/</x:v>
       </x:c>
       <x:c r="J27" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>送付可（英語）</x:v>
       </x:c>
       <x:c r="K27" s="8" t="str">
         <x:v>S3</x:v>
@@ -1344,7 +1344,7 @@
       </x:c>
       <x:c r="O27" s="8" t="str"/>
       <x:c r="P27" s="8" t="str">
-        <x:v>英語版プレスリリースを用意した段階で候補</x:v>
+        <x:v>PC・日本のゲームを扱う英語メディア。英語版で送付</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -1376,7 +1376,7 @@
         <x:v>https://gamewith.jp/</x:v>
       </x:c>
       <x:c r="J28" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>よくわからない</x:v>
       </x:c>
       <x:c r="K28" s="8" t="str">
         <x:v>S6</x:v>
@@ -1389,7 +1389,9 @@
         <x:v>未確認</x:v>
       </x:c>
       <x:c r="O28" s="8" t="str"/>
-      <x:c r="P28" s="8" t="str"/>
+      <x:c r="P28" s="8" t="str">
+        <x:v>公式メディ窓口はあるが、開発者からのプレスリリース受付を明記していない</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="7" t="str">
@@ -1460,13 +1462,13 @@
         <x:v>pub_cruise@hotmail.com</x:v>
       </x:c>
       <x:c r="H30" s="8" t="str">
-        <x:v>https://enterjam.com/</x:v>
+        <x:v>https://enterjam.com/運営会社ご案内</x:v>
       </x:c>
       <x:c r="I30" s="8" t="str">
         <x:v>https://enterjam.com/</x:v>
       </x:c>
       <x:c r="J30" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>送付可</x:v>
       </x:c>
       <x:c r="K30" s="8" t="str">
         <x:v>S2 / S5</x:v>
@@ -1480,7 +1482,7 @@
       </x:c>
       <x:c r="O30" s="8" t="str"/>
       <x:c r="P30" s="8" t="str">
-        <x:v>2026年の実送付例に含まれる</x:v>
+        <x:v>公式運営会社ページでプレスリリース送付先を確認。2026-09-16確認</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -1506,13 +1508,13 @@
         <x:v>公式フォーム</x:v>
       </x:c>
       <x:c r="H31" s="8" t="str">
-        <x:v>https://cste.co.jp/release/</x:v>
+        <x:v>https://cste.co.jp/contact/otakei/release.html</x:v>
       </x:c>
       <x:c r="I31" s="8" t="str">
         <x:v>https://otakei.otakuma.net/</x:v>
       </x:c>
       <x:c r="J31" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>送付可</x:v>
       </x:c>
       <x:c r="K31" s="8" t="str">
         <x:v>S3</x:v>
@@ -1525,7 +1527,9 @@
         <x:v>未確認</x:v>
       </x:c>
       <x:c r="O31" s="8" t="str"/>
-      <x:c r="P31" s="8" t="str"/>
+      <x:c r="P31" s="8" t="str">
+        <x:v>公式フォームで受付。団体情報・電話番号が必須</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="24" hidden="0" customHeight="1">
       <x:c r="A32" s="7" t="str">
@@ -1556,7 +1560,7 @@
         <x:v>https://doope.jp/</x:v>
       </x:c>
       <x:c r="J32" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>送付可</x:v>
       </x:c>
       <x:c r="K32" s="8" t="str">
         <x:v>S7 / S8</x:v>
@@ -1570,7 +1574,7 @@
       </x:c>
       <x:c r="O32" s="8" t="str"/>
       <x:c r="P32" s="8" t="str">
-        <x:v>共有表には2024年時点でメンテナンス中との注記あり</x:v>
+        <x:v>公式フォームはメンテナンス中。添付ファイルがある場合は doopeinfo@gmail.com へ送付</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="24" hidden="0" customHeight="1">
@@ -1596,13 +1600,13 @@
         <x:v>release@ascii.jp</x:v>
       </x:c>
       <x:c r="H33" s="8" t="str">
-        <x:v>https://ascii.jp/</x:v>
+        <x:v>https://ascii.jp/support/</x:v>
       </x:c>
       <x:c r="I33" s="8" t="str">
         <x:v>https://ascii.jp/</x:v>
       </x:c>
       <x:c r="J33" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>送付可</x:v>
       </x:c>
       <x:c r="K33" s="8" t="str">
         <x:v>S7</x:v>
@@ -1616,7 +1620,7 @@
       </x:c>
       <x:c r="O33" s="8" t="str"/>
       <x:c r="P33" s="8" t="str">
-        <x:v>ゲーム専門媒体ではない</x:v>
+        <x:v>公式サポートと公式チャンネル案内で release@ascii.jp を確認</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="24" hidden="0" customHeight="1">
@@ -1689,18 +1693,20 @@
       <x:c r="G35" s="8" t="str">
         <x:v>press@game8.jp</x:v>
       </x:c>
-      <x:c r="H35" s="8" t="str"/>
+      <x:c r="H35" s="8" t="str">
+        <x:v>https://game8.jp/press</x:v>
+      </x:c>
       <x:c r="I35" s="8" t="str">
         <x:v>https://game8.jp/</x:v>
       </x:c>
       <x:c r="J35" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>送付可</x:v>
       </x:c>
       <x:c r="K35" s="8" t="str">
         <x:v>S8</x:v>
       </x:c>
       <x:c r="L35" s="8" t="str">
-        <x:v>未送付</x:v>
+        <x:v>今回は見送り</x:v>
       </x:c>
       <x:c r="M35" s="9"/>
       <x:c r="N35" s="8" t="str">
@@ -1708,7 +1714,7 @@
       </x:c>
       <x:c r="O35" s="8" t="str"/>
       <x:c r="P35" s="8" t="str">
-        <x:v>共有表では大手タイトル中心との注記あり</x:v>
+        <x:v>公式のプレスリリース受付あり。2026-09-16、ユーザー判断により今回は送付見送り</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
@@ -1740,7 +1746,7 @@
         <x:v>https://mudauchi.info/</x:v>
       </x:c>
       <x:c r="J36" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>送付可</x:v>
       </x:c>
       <x:c r="K36" s="8" t="str">
         <x:v>S8</x:v>
@@ -1754,7 +1760,7 @@
       </x:c>
       <x:c r="O36" s="8" t="str"/>
       <x:c r="P36" s="8" t="str">
-        <x:v>共有表ではインディー歓迎・対応が早いとの記録</x:v>
+        <x:v>インディーズ・個人も受付可を明記。Steam作品の掲載実績あり</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
@@ -1826,13 +1832,13 @@
         <x:v>news-pr@mynavi.jp</x:v>
       </x:c>
       <x:c r="H38" s="8" t="str">
-        <x:v>https://news.mynavi.jp/top/notice/press.html</x:v>
+        <x:v>https://news.mynavi.jp/top/notice/press/</x:v>
       </x:c>
       <x:c r="I38" s="8" t="str">
         <x:v>https://news.mynavi.jp/</x:v>
       </x:c>
       <x:c r="J38" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>送付可</x:v>
       </x:c>
       <x:c r="K38" s="8" t="str">
         <x:v>S2 / S7</x:v>
@@ -1846,7 +1852,7 @@
       </x:c>
       <x:c r="O38" s="8" t="str"/>
       <x:c r="P38" s="8" t="str">
-        <x:v>ゲーム専門媒体ではない</x:v>
+        <x:v>公式のプレスリリース窓口を確認</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
@@ -1878,7 +1884,7 @@
         <x:v>https://otakuindustry.biz/</x:v>
       </x:c>
       <x:c r="J39" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>送付可</x:v>
       </x:c>
       <x:c r="K39" s="8" t="str">
         <x:v>S2 / S3 / S7</x:v>
@@ -1891,7 +1897,9 @@
         <x:v>未確認</x:v>
       </x:c>
       <x:c r="O39" s="8" t="str"/>
-      <x:c r="P39" s="8" t="str"/>
+      <x:c r="P39" s="8" t="str">
+        <x:v>公式窓口でレビュー依頼・プレスリリースを受付</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
       <x:c r="A40" s="7" t="str">
@@ -1916,13 +1924,13 @@
         <x:v>press@rocketnews24.com</x:v>
       </x:c>
       <x:c r="H40" s="8" t="str">
-        <x:v>https://rocketnews24.com/</x:v>
+        <x:v>https://rocketnews24.com/pr-2/</x:v>
       </x:c>
       <x:c r="I40" s="8" t="str">
         <x:v>https://rocketnews24.com/</x:v>
       </x:c>
       <x:c r="J40" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>よくわからない</x:v>
       </x:c>
       <x:c r="K40" s="8" t="str">
         <x:v>S7</x:v>
@@ -1936,7 +1944,7 @@
       </x:c>
       <x:c r="O40" s="8" t="str"/>
       <x:c r="P40" s="8" t="str">
-        <x:v>ゲーム専門媒体ではない</x:v>
+        <x:v>現在の公式プレスリリース送付先を確認できず。既存メールは旧資料由来</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="15" hidden="0" customHeight="1">
@@ -1968,7 +1976,7 @@
         <x:v>http://vsmedia.info/</x:v>
       </x:c>
       <x:c r="J41" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>よくわからない</x:v>
       </x:c>
       <x:c r="K41" s="8" t="str">
         <x:v>S3</x:v>
@@ -1982,7 +1990,7 @@
       </x:c>
       <x:c r="O41" s="8" t="str"/>
       <x:c r="P41" s="8" t="str">
-        <x:v>受付状況の再確認が必要</x:v>
+        <x:v>現行の受付案内と連絡先を確認できず</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -2008,13 +2016,13 @@
         <x:v>公式案内を確認</x:v>
       </x:c>
       <x:c r="H42" s="8" t="str">
-        <x:v>https://markelabo.com/all</x:v>
+        <x:v>https://markelabo.com/</x:v>
       </x:c>
       <x:c r="I42" s="8" t="str">
         <x:v>https://markelabo.com/all</x:v>
       </x:c>
       <x:c r="J42" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>対象外（現段階）</x:v>
       </x:c>
       <x:c r="K42" s="8" t="str">
         <x:v>S7 / S8</x:v>
@@ -2028,7 +2036,7 @@
       </x:c>
       <x:c r="O42" s="8" t="str"/>
       <x:c r="P42" s="8" t="str">
-        <x:v>TGS出展の成果やマーケティング事例ができた後の候補</x:v>
+        <x:v>一般的なリリース窓口ではなく、プロダクト運営・成長事例の取材相談向け</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
@@ -2060,7 +2068,7 @@
         <x:v>https://appmedia.jp/</x:v>
       </x:c>
       <x:c r="J43" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>送付可</x:v>
       </x:c>
       <x:c r="K43" s="8" t="str">
         <x:v>S2 / S7 / S8</x:v>
@@ -2074,7 +2082,7 @@
       </x:c>
       <x:c r="O43" s="8" t="str"/>
       <x:c r="P43" s="8" t="str">
-        <x:v>NyctoTypeはPC向けのため優先度低め</x:v>
+        <x:v>公式のリリース投稿フォームあり。2026年にSteamインディー作品の掲載実績あり</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="24" hidden="0" customHeight="1">
@@ -2100,13 +2108,13 @@
         <x:v>公式フォーム</x:v>
       </x:c>
       <x:c r="H44" s="8" t="str">
-        <x:v>https://docs.google.com/forms/d/e/1FAIpQLSc9C3DbtdOoQ1pf0JiIxy8zoE7AKZAC8v7ciMchsaDzecjiEw/viewform</x:v>
+        <x:v>https://game.boom-app.com/</x:v>
       </x:c>
       <x:c r="I44" s="8" t="str">
         <x:v>https://game.boom-app.com/</x:v>
       </x:c>
       <x:c r="J44" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>対象外（現状）</x:v>
       </x:c>
       <x:c r="K44" s="8" t="str">
         <x:v>S2 / S7 / S8</x:v>
@@ -2120,7 +2128,7 @@
       </x:c>
       <x:c r="O44" s="8" t="str"/>
       <x:c r="P44" s="8" t="str">
-        <x:v>NyctoTypeはPC向けのため優先度低め</x:v>
+        <x:v>現サイトはゲームニュース中心ではなく、現行のリリース受付も確認できず</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -2146,13 +2154,13 @@
         <x:v>gameapp-press@ma-inc.jp</x:v>
       </x:c>
       <x:c r="H45" s="8" t="str">
-        <x:v>https://www.ma-inc.jp/report/</x:v>
+        <x:v>https://ma-inc.jp/game_support/game_appli_info/press1355/</x:v>
       </x:c>
       <x:c r="I45" s="8" t="str">
         <x:v>https://www.ma-inc.jp/report/</x:v>
       </x:c>
       <x:c r="J45" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>受付終了</x:v>
       </x:c>
       <x:c r="K45" s="8" t="str">
         <x:v>S7 / S8</x:v>
@@ -2166,7 +2174,7 @@
       </x:c>
       <x:c r="O45" s="8" t="str"/>
       <x:c r="P45" s="8" t="str">
-        <x:v>NyctoTypeはPC向けのため優先度低め</x:v>
+        <x:v>2025年12月に更新終了、2026年1月にサイト閉鎖</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
@@ -2198,7 +2206,7 @@
         <x:v>https://app.famitsu.com/</x:v>
       </x:c>
       <x:c r="J46" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>対象外（PC専用）</x:v>
       </x:c>
       <x:c r="K46" s="8" t="str">
         <x:v>S2 / S7 / S8</x:v>
@@ -2212,7 +2220,7 @@
       </x:c>
       <x:c r="O46" s="8" t="str"/>
       <x:c r="P46" s="8" t="str">
-        <x:v>将来モバイル展開がない限り見送り候補</x:v>
+        <x:v>現行公式連絡先にファミ通App用リリース窓口なし。モバイル向け</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -2244,7 +2252,7 @@
         <x:v>https://www.appbank.net/</x:v>
       </x:c>
       <x:c r="J47" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>送付可</x:v>
       </x:c>
       <x:c r="K47" s="8" t="str">
         <x:v>S7 / S8</x:v>
@@ -2258,7 +2266,7 @@
       </x:c>
       <x:c r="O47" s="8" t="str"/>
       <x:c r="P47" s="8" t="str">
-        <x:v>共有リスト間で宛先表記が異なるため送付前確認</x:v>
+        <x:v>公式ページで pressrelease@appbank.net を確認。PCゲームとの相性は低め</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -2284,13 +2292,13 @@
         <x:v>レビュー依頼フォーム</x:v>
       </x:c>
       <x:c r="H48" s="8" t="str">
-        <x:v>https://app-liv.jp/contact/review_request/</x:v>
+        <x:v>https://app-liv.jp/contact/</x:v>
       </x:c>
       <x:c r="I48" s="8" t="str">
         <x:v>https://app-liv.jp/</x:v>
       </x:c>
       <x:c r="J48" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>対象外（PC専用）</x:v>
       </x:c>
       <x:c r="K48" s="8" t="str">
         <x:v>S2 / S7 / S8</x:v>
@@ -2304,7 +2312,7 @@
       </x:c>
       <x:c r="O48" s="8" t="str"/>
       <x:c r="P48" s="8" t="str">
-        <x:v>PC専用ゲームは対象外の可能性が高い</x:v>
+        <x:v>App Store・Google Play掲載アプリのレビュー依頼向け</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -2336,7 +2344,7 @@
         <x:v>https://appget.com/</x:v>
       </x:c>
       <x:c r="J49" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>対象外（PC専用）</x:v>
       </x:c>
       <x:c r="K49" s="8" t="str">
         <x:v>S2 / S7 / S8</x:v>
@@ -2350,7 +2358,7 @@
       </x:c>
       <x:c r="O49" s="8" t="str"/>
       <x:c r="P49" s="8" t="str">
-        <x:v>PC専用ゲームは対象外の可能性が高い</x:v>
+        <x:v>受付窓口は有効だが、スマートフォンアプリ向け</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -2376,13 +2384,13 @@
         <x:v>公式フォーム</x:v>
       </x:c>
       <x:c r="H50" s="8" t="str">
-        <x:v>https://altema.jp/contact</x:v>
+        <x:v>https://altema.jp/contact-interview</x:v>
       </x:c>
       <x:c r="I50" s="8" t="str">
         <x:v>https://altema.jp/</x:v>
       </x:c>
       <x:c r="J50" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>よくわからない</x:v>
       </x:c>
       <x:c r="K50" s="8" t="str">
         <x:v>S7 / S8</x:v>
@@ -2395,7 +2403,9 @@
         <x:v>未確認</x:v>
       </x:c>
       <x:c r="O50" s="8" t="str"/>
-      <x:c r="P50" s="8" t="str"/>
+      <x:c r="P50" s="8" t="str">
+        <x:v>取材・インタビュー受付は確認。一般的なプレスリリース受付は不明</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
       <x:c r="A51" s="7" t="str">
@@ -2426,7 +2436,7 @@
         <x:v>https://kamigame.jp/</x:v>
       </x:c>
       <x:c r="J51" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>よくわからない</x:v>
       </x:c>
       <x:c r="K51" s="8" t="str">
         <x:v>S7</x:v>
@@ -2440,7 +2450,7 @@
       </x:c>
       <x:c r="O51" s="8" t="str"/>
       <x:c r="P51" s="8" t="str">
-        <x:v>PC専用ゲームは優先度低め</x:v>
+        <x:v>開発者向けの情報提供・プレスリリース窓口を確認できず</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -2472,7 +2482,7 @@
         <x:v>https://www.gapsis.jp/</x:v>
       </x:c>
       <x:c r="J52" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>対象外（PC専用）</x:v>
       </x:c>
       <x:c r="K52" s="8" t="str">
         <x:v>S7</x:v>
@@ -2486,7 +2496,7 @@
       </x:c>
       <x:c r="O52" s="8" t="str"/>
       <x:c r="P52" s="8" t="str">
-        <x:v>PC専用ゲームは優先度低め</x:v>
+        <x:v>Android関連の製品・サービスのみ受付</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -2512,13 +2522,13 @@
         <x:v>applion.press@gmail.com</x:v>
       </x:c>
       <x:c r="H53" s="8" t="str">
-        <x:v>https://applion.jp/about</x:v>
+        <x:v>https://applion.jp/about/</x:v>
       </x:c>
       <x:c r="I53" s="8" t="str">
         <x:v>https://applion.jp/</x:v>
       </x:c>
       <x:c r="J53" s="8" t="str">
-        <x:v>送付前に確認</x:v>
+        <x:v>対象外（PC専用）</x:v>
       </x:c>
       <x:c r="K53" s="8" t="str">
         <x:v>S7</x:v>
@@ -2532,7 +2542,7 @@
       </x:c>
       <x:c r="O53" s="8" t="str"/>
       <x:c r="P53" s="8" t="str">
-        <x:v>PC専用ゲームは対象外の可能性が高い</x:v>
+        <x:v>App Store・Google Playのスマートフォンアプリ専門</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -3007,7 +3017,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb059ed97745a46ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9810ad1761243c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3248,7 +3258,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c7621e53d044599"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9929a2bae64445b"/>
   </x:tableParts>
 </x:worksheet>
 </file>